--- a/backtest_runs/20260410_193731/by_symbol/LSEFSL/LSEFSL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/LSEFSL/LSEFSL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -771,7 +771,7 @@
         <v>-4003.200000000003</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>100834</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>101084.2</v>
@@ -1047,7 +1047,7 @@
         <v>-8506.799999999996</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>92577.39999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-7589.400000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>92744.2</v>
@@ -1277,7 +1277,7 @@
         <v>-83.39999999999822</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>92660.79999999999</v>
@@ -1369,7 +1369,7 @@
         <v>-750.5999999999988</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>91910.2</v>
@@ -1461,7 +1461,7 @@
         <v>-2418.600000000008</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>91076.2</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>107506</v>
